--- a/aq_files/0671.xlsx
+++ b/aq_files/0671.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,888 +413,573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Options (if MCQ)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Typical DW architecture has:</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2 layers</t>
+          <t>Which orchestration tool is built into Docker?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3 layers</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4 layers</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5 layers</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bottom layer includes:</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dashboards</t>
+          <t>Kubernetes was originally developed by __________.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data sources</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UIs</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Middle layer typically hosts:</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OLAP server</t>
+          <t>Which tool has steeper learning curve?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>A) Docker Swarm B) Kubernetes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Compiler</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Top layer provides:</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Scenario: You need advanced autoscaling and complex networking. Which should you choose?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>User interface</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Indexing</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Staging area is used for:</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visualization</t>
+          <t>True or False: Docker Swarm supports rolling updates.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Temporary processing/cleaning</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>A) True B) False</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETL belongs to:</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Which tool uses YAML manifests called "Compose files" for Swarm?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data storage occurs in:</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Kubernetes uses __________ for service discovery by default.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OLAP is used for:</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transactions</t>
+          <t>Swarm's native load balancing is __________ (L3/L4/L7).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compilation</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data cube enables:</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Single-dimension queries</t>
+          <t>Command to initialize a Docker Swarm cluster?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Multi-dimensional analysis</t>
+          <t>Command</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Storage only</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Security only</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Practical</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Metadata repository stores:</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raw data</t>
+          <t>Which tool has a larger community and ecosystem?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Data about data</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Logs only</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Transformations occur in:</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Scenario: You have a small team and simple microservices (5-10). Which is easier to operate?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reporting tools belong to:</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Kubernetes uses __________ as its node agent.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Centralized architecture uses:</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Multiple repos</t>
+          <t>True or False: Swarm uses etcd for consistent storage.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Single repository</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No storage</t>
+          <t>A) True B) False</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Edge only</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Most scalable approach:</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Centralized</t>
+          <t>Which tool supports built-in secrets management without additional components?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Distributed</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>A) Both B) Swarm only C) Kubernetes only</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data from ERP/CRM is cleaned before loading. Which layer handles this?</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Command to deploy a stack in Swarm?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Middle (ETL)</t>
+          <t>Command</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Practical</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Users view dashboards and reports. Which layer?</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Kubernetes Ingress operates at which layer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Temporary holding area before transformation is called:</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Scenario: You need GPU scheduling and batch jobs. Which tool is better?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Staging area</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cache</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lake</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System needs scaling across regions. Choose architecture:</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Centralized</t>
+          <t>Which tool was declared "production-ready" first?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Distributed</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>A) Swarm B) Kubernetes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monolith</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytical engine executing cube queries is:</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OLTP server</t>
+          <t>Swarm's service mesh is called __________.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OLAP server</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Web server</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Department-specific subsets integrated into architecture are:</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Data marts</t>
+          <t>True or False: You can run Kubernetes on top of Swarm.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Caches</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Logs</t>
+          <t>A) True B) False</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Queues</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
